--- a/data/ggiliberti.xlsx
+++ b/data/ggiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{7C72F743-D517-44F0-9882-C2F252CF56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CC335AC-43EB-4654-86F8-8BCA310952FC}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{7C72F743-D517-44F0-9882-C2F252CF56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A638FA0-CB58-4929-9818-7F3BDF41A269}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33C575A0-9228-4950-866C-B1793985D5A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D5B252-887C-4B48-B556-C9D8159FD44D}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="8"/>
@@ -3353,35 +3353,219 @@
         <v>15</v>
       </c>
       <c r="D62" s="4">
-        <f t="shared" ref="D62" si="98">+D61+K61+E61-F62</f>
+        <f t="shared" ref="D62:D66" si="98">+D61+K61+E61-F62</f>
         <v>18277.740000000002</v>
+      </c>
+      <c r="G62" s="4">
+        <v>255.89</v>
       </c>
       <c r="H62" s="5">
         <f t="shared" si="92"/>
-        <v>30308.599999999995</v>
+        <v>30564.489999999994</v>
       </c>
       <c r="I62" s="5">
         <f t="shared" si="93"/>
-        <v>0</v>
+        <v>25.588999999999999</v>
       </c>
       <c r="J62" s="5">
         <f t="shared" si="6"/>
-        <v>3030.8600000000006</v>
+        <v>3056.4490000000005</v>
       </c>
       <c r="K62" s="5">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>230.30099999999999</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="95"/>
-        <v>27277.74</v>
+        <v>27508.041000000001</v>
       </c>
       <c r="M62" s="5">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>7.6766999999999994</v>
       </c>
       <c r="N62" s="6">
         <f t="shared" si="97"/>
+        <v>1.4000089726629221E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>45917</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="4">
+        <f t="shared" si="98"/>
+        <v>18508.041000000001</v>
+      </c>
+      <c r="G63" s="4">
+        <v>425.68</v>
+      </c>
+      <c r="H63" s="5">
+        <f t="shared" ref="H63:H66" si="99">+H62+G63</f>
+        <v>30990.169999999995</v>
+      </c>
+      <c r="I63" s="5">
+        <f t="shared" ref="I63:I66" si="100">+G63*0.1</f>
+        <v>42.568000000000005</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" ref="J63:J66" si="101">+J62+I63</f>
+        <v>3099.0170000000007</v>
+      </c>
+      <c r="K63" s="5">
+        <f t="shared" ref="K63:K66" si="102">+G63-I63</f>
+        <v>383.11200000000002</v>
+      </c>
+      <c r="L63" s="5">
+        <f t="shared" ref="L63:L66" si="103">+L62+K63</f>
+        <v>27891.153000000002</v>
+      </c>
+      <c r="M63" s="5">
+        <f t="shared" ref="M63:M66" si="104">+K63/30</f>
+        <v>12.7704</v>
+      </c>
+      <c r="N63" s="6">
+        <f t="shared" ref="N63:N66" si="105">+G63/D63</f>
+        <v>2.2999732926893775E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="4">
+        <f t="shared" si="98"/>
+        <v>18891.153000000002</v>
+      </c>
+      <c r="G64" s="4">
+        <v>396.71</v>
+      </c>
+      <c r="H64" s="5">
+        <f t="shared" si="99"/>
+        <v>31386.879999999994</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" si="100"/>
+        <v>39.670999999999999</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="101"/>
+        <v>3138.6880000000006</v>
+      </c>
+      <c r="K64" s="5">
+        <f t="shared" si="102"/>
+        <v>357.03899999999999</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" si="103"/>
+        <v>28248.192000000003</v>
+      </c>
+      <c r="M64" s="5">
+        <f t="shared" si="104"/>
+        <v>11.901299999999999</v>
+      </c>
+      <c r="N64" s="6">
+        <f t="shared" si="105"/>
+        <v>2.0999776985555087E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>45978</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="4">
+        <f t="shared" si="98"/>
+        <v>19248.192000000003</v>
+      </c>
+      <c r="G65" s="4">
+        <v>692.93</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" si="99"/>
+        <v>32079.809999999994</v>
+      </c>
+      <c r="I65" s="5">
+        <f t="shared" si="100"/>
+        <v>69.292999999999992</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="101"/>
+        <v>3207.9810000000007</v>
+      </c>
+      <c r="K65" s="5">
+        <f t="shared" si="102"/>
+        <v>623.63699999999994</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" si="103"/>
+        <v>28871.829000000002</v>
+      </c>
+      <c r="M65" s="5">
+        <f t="shared" si="104"/>
+        <v>20.787899999999997</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" si="105"/>
+        <v>3.5999744807200584E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>46008</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="4">
+        <f t="shared" si="98"/>
+        <v>19871.829000000002</v>
+      </c>
+      <c r="H66" s="5">
+        <f t="shared" si="99"/>
+        <v>32079.809999999994</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="101"/>
+        <v>3207.9810000000007</v>
+      </c>
+      <c r="K66" s="5">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <f t="shared" si="103"/>
+        <v>28871.829000000002</v>
+      </c>
+      <c r="M66" s="5">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="N66" s="6">
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
     </row>

--- a/data/ggiliberti.xlsx
+++ b/data/ggiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{7C72F743-D517-44F0-9882-C2F252CF56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A638FA0-CB58-4929-9818-7F3BDF41A269}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{7C72F743-D517-44F0-9882-C2F252CF56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03CCEC27-F89B-41D6-B2F1-2E7B7EE9375B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33C575A0-9228-4950-866C-B1793985D5A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D5B252-887C-4B48-B556-C9D8159FD44D}">
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="8"/>
@@ -3540,33 +3540,174 @@
         <f t="shared" si="98"/>
         <v>19871.829000000002</v>
       </c>
+      <c r="G66" s="4">
+        <v>254.02</v>
+      </c>
       <c r="H66" s="5">
         <f t="shared" si="99"/>
-        <v>32079.809999999994</v>
+        <v>32333.829999999994</v>
       </c>
       <c r="I66" s="5">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>25.402000000000001</v>
       </c>
       <c r="J66" s="5">
         <f t="shared" si="101"/>
-        <v>3207.9810000000007</v>
+        <v>3233.3830000000007</v>
       </c>
       <c r="K66" s="5">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>228.61799999999999</v>
       </c>
       <c r="L66" s="5">
         <f t="shared" si="103"/>
-        <v>28871.829000000002</v>
+        <v>29100.447</v>
       </c>
       <c r="M66" s="5">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>7.6205999999999996</v>
       </c>
       <c r="N66" s="6">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1.2782919981849682E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <v>46039</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="4">
+        <f t="shared" ref="D67:D69" si="106">+D66+K66+E66-F67</f>
+        <v>20100.447</v>
+      </c>
+      <c r="G67" s="4">
+        <v>135.44999999999999</v>
+      </c>
+      <c r="H67" s="5">
+        <f t="shared" ref="H67:H69" si="107">+H66+G67</f>
+        <v>32469.279999999995</v>
+      </c>
+      <c r="I67" s="5">
+        <f t="shared" ref="I67:I69" si="108">+G67*0.1</f>
+        <v>13.545</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" ref="J67:J69" si="109">+J66+I67</f>
+        <v>3246.9280000000008</v>
+      </c>
+      <c r="K67" s="5">
+        <f t="shared" ref="K67:K69" si="110">+G67-I67</f>
+        <v>121.90499999999999</v>
+      </c>
+      <c r="L67" s="5">
+        <f t="shared" ref="L67:L69" si="111">+L66+K67</f>
+        <v>29222.351999999999</v>
+      </c>
+      <c r="M67" s="5">
+        <f t="shared" ref="M67:M69" si="112">+K67/30</f>
+        <v>4.0634999999999994</v>
+      </c>
+      <c r="N67" s="6">
+        <f t="shared" ref="N67:N69" si="113">+G67/D67</f>
+        <v>6.7386561104835129E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>46070</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="4">
+        <f t="shared" si="106"/>
+        <v>20222.351999999999</v>
+      </c>
+      <c r="G68" s="4">
+        <v>480.92</v>
+      </c>
+      <c r="H68" s="5">
+        <f t="shared" si="107"/>
+        <v>32950.199999999997</v>
+      </c>
+      <c r="I68" s="5">
+        <f t="shared" si="108"/>
+        <v>48.092000000000006</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="109"/>
+        <v>3295.0200000000009</v>
+      </c>
+      <c r="K68" s="5">
+        <f t="shared" si="110"/>
+        <v>432.82800000000003</v>
+      </c>
+      <c r="L68" s="5">
+        <f t="shared" si="111"/>
+        <v>29655.18</v>
+      </c>
+      <c r="M68" s="5">
+        <f t="shared" si="112"/>
+        <v>14.427600000000002</v>
+      </c>
+      <c r="N68" s="6">
+        <f t="shared" si="113"/>
+        <v>2.3781605621344147E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>46098</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="4">
+        <f t="shared" si="106"/>
+        <v>20655.18</v>
+      </c>
+      <c r="G69" s="4">
+        <v>375.77</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" si="107"/>
+        <v>33325.969999999994</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" si="108"/>
+        <v>37.576999999999998</v>
+      </c>
+      <c r="J69" s="5">
+        <f t="shared" si="109"/>
+        <v>3332.5970000000007</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="110"/>
+        <v>338.19299999999998</v>
+      </c>
+      <c r="L69" s="5">
+        <f t="shared" si="111"/>
+        <v>29993.373</v>
+      </c>
+      <c r="M69" s="5">
+        <f t="shared" si="112"/>
+        <v>11.273099999999999</v>
+      </c>
+      <c r="N69" s="6">
+        <f t="shared" si="113"/>
+        <v>1.8192530880873466E-2</v>
       </c>
     </row>
   </sheetData>
